--- a/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -476,72 +476,72 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[인터뷰] 황현선 "민주당, 합당 원하면 사과부터…아니면 약탈 정치"</t>
+          <t>윤석열 ‘유죄’ 나온 명태균 여론조사…김건희·오세훈에도 영향 미칠...</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059819?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003458190?sid=102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>"11년 묶인 담뱃값, 사실상 내린 셈…일회성 아닌 지속 인상"</t>
+          <t>“집회 오라” 전화 거는 장동혁 측근들, 전화 피하는 의원들</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059818?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003537661?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>당신의 ‘생각’은 안녕하신가요[신간]</t>
+          <t>장동혁·정점식, 모처럼 '보완수사권' 한뜻… 한동훈까지 단일대오 움직...</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/033/0000051342?sid=103</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942308?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[사설] 생활 밀착 공약, 이제는 '실행력'으로 답해야</t>
+          <t>송영길 "정청래, 대선 출마 안 한다? 누가 출마하랬나"</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.cctoday.co.kr/news/articleView.html?idxno=2233268</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002448429?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[허정수칼럼] 호남 반도체 논란, 삼성·SK가 답할 차례</t>
+          <t>김민석 "지난 1년간 당정관계 잘 안 돼, 당대표 자기 정치 때문"</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/293/0000087639?sid=110</t>
+          <t>https://n.news.naver.com/mnews/article/002/0002448428?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[기자의눈] 제2의 장윤기 사건이 나오지 않으려면</t>
+          <t>오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://www.ajunews.com/view/20260714031707434</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
         </is>
       </c>
     </row>
@@ -555,36 +555,36 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>대전 원도심 공약 '경제 회복' 초점 [지방의원 공약추적단 시즌2]</t>
+          <t>‘조국당과 합당 무산’ 김민석에 화살 돌리는 정청래</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>https://www.cctoday.co.kr/news/articleView.html?idxno=2233262</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003733978?sid=100</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>‘서울대와 협업(UP)’ 관악S밸리 고도화…“벤처창업도시로 질적 도약...</t>
+          <t>정청래 “보완수사권 존치론 당황”…당 정체성·검찰개혁 강조</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>https://www.etoday.co.kr/news/view/2603527</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006330307?sid=100</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>코인 현물 ETF 밑그림 나왔다…"김프 없애고 선물시장 도입"</t>
+          <t>정청래, '보완수사권 일부 존치' 제기에 "정말 손 많이 가는 당"</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016194810?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009059665?sid=100</t>
         </is>
       </c>
     </row>
@@ -598,36 +598,36 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[오늘의 주요일정]사회(7월15일 수요일)</t>
+          <t>[단독] 장동혁, 경기도당 위원장으로 '최측근' 조광한 띄우기, 당권파 세...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067086?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/469/0000942299?sid=100</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>[헐크 이만수의 힘] 아시아 야구의 새로운 지평, 이윤 대표와 함께 걷는...</t>
+          <t>장동혁, '재선거' 고리로 전국 돌며 지지층 확보 총력…오늘 광주행</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>https://www.nbntv.co.kr/news/articleView.html?idxno=4023002</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014067055?sid=100</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>반도체만 잘 나갔다…고용절벽에 꺼낸 '20만 AI 인재' 카드</t>
+          <t>오세훈 “부동산 한말씀 드려도 되겠나” 한성숙 “서류로 받겠다”</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005386139?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003733968?sid=100</t>
         </is>
       </c>
     </row>
@@ -641,36 +641,36 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>“무역장벽 제거되면 對中 화장품 수출 27% ↑”</t>
+          <t>[단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://www.yakup.com/news/index.html?mode=view&amp;cat=12&amp;nid=329780</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003458192?sid=102</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>빚에 쫓기는 위기가구 찾는다…불법사금융 피해 정보 연계</t>
+          <t>수출 4강 '가시권'·소득 5만불 '환율 변수'…잠재성장 3%는 '험로'</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067095?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009059814?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
+          <t>"교사·학생도 경제·금융 알아야"…서울교육청, 연수·수업 연계</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458192?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014067116?sid=102</t>
         </is>
       </c>
     </row>

--- a/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -476,7 +476,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>윤석열 ‘유죄’ 나온 명태균 여론조사…김건희·오세훈에도 영향 미칠...</t>
+          <t>[경향신문] 윤석열 ‘유죄’ 나온 명태균 여론조사…김건희·오세훈에도 영향 미칠...</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>“집회 오라” 전화 거는 장동혁 측근들, 전화 피하는 의원들</t>
+          <t>[중앙일보] “집회 오라” 전화 거는 장동혁 측근들, 전화 피하는 의원들</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -500,7 +500,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>장동혁·정점식, 모처럼 '보완수사권' 한뜻… 한동훈까지 단일대오 움직...</t>
+          <t>[한국일보] 장동혁·정점식, 모처럼 '보완수사권' 한뜻… 한동훈까지 단일대오 움직...</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -512,36 +512,36 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>송영길 "정청래, 대선 출마 안 한다? 누가 출마하랬나"</t>
+          <t>[조선일보] 버티던 정청래, 선호투표 수용… 친명 “동정표 노리고 선회”</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002448429?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987664?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>김민석 "지난 1년간 당정관계 잘 안 돼, 당대표 자기 정치 때문"</t>
+          <t>[조선일보] 오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/002/0002448428?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
+          <t>[문화일보] 박범계 “정청래, 누구보다 사나워…스스로 약자 표현 적절치 않아”</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/021/0002804698?sid=100</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>‘조국당과 합당 무산’ 김민석에 화살 돌리는 정청래</t>
+          <t>[동아일보] ‘조국당과 합당 무산’ 김민석에 화살 돌리는 정청래</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>정청래 “보완수사권 존치론 당황”…당 정체성·검찰개혁 강조</t>
+          <t>[이데일리] 정청래 “보완수사권 존치론 당황”…당 정체성·검찰개혁 강조</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>정청래, '보완수사권 일부 존치' 제기에 "정말 손 많이 가는 당"</t>
+          <t>[뉴스1] 정청래, '보완수사권 일부 존치' 제기에 "정말 손 많이 가는 당"</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>[단독] 장동혁, 경기도당 위원장으로 '최측근' 조광한 띄우기, 당권파 세...</t>
+          <t>[한국일보] [단독] 장동혁, 경기도당 위원장으로 '최측근' 조광한 띄우기, 당권파 세...</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -610,7 +610,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>장동혁, '재선거' 고리로 전국 돌며 지지층 확보 총력…오늘 광주행</t>
+          <t>[뉴시스] 장동혁, '재선거' 고리로 전국 돌며 지지층 확보 총력…오늘 광주행</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>오세훈 “부동산 한말씀 드려도 되겠나” 한성숙 “서류로 받겠다”</t>
+          <t>[동아일보] 오세훈 “부동산 한말씀 드려도 되겠나” 한성숙 “서류로 받겠다”</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
+          <t>[경향신문] [단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -653,24 +653,24 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>수출 4강 '가시권'·소득 5만불 '환율 변수'…잠재성장 3%는 '험로'</t>
+          <t>[경향신문] ‘한국 가면 여행가방 가득 화장품’···내수 소비 끌어올린 건 알고...</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059814?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/032/0003458196?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>"교사·학생도 경제·금융 알아야"…서울교육청, 연수·수업 연계</t>
+          <t>[머니투데이] 계좌 파랗게 질려도 '월 500만원' 따박따박…폭락장 버틴 50대의 비결</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067116?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005386148?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -512,24 +512,24 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 버티던 정청래, 선호투표 수용… 친명 “동정표 노리고 선회”</t>
+          <t>[조선일보] 오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987664?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
+          <t>[조선일보] 버티던 정청래, 선호투표 수용… 친명 “동정표 노리고 선회”</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987664?sid=100</t>
         </is>
       </c>
     </row>
@@ -653,24 +653,24 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] ‘한국 가면 여행가방 가득 화장품’···내수 소비 끌어올린 건 알고...</t>
+          <t>[뉴시스] "교사·학생도 경제·금융 알아야"…서울교육청, 연수·수업 연계</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458196?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014067116?sid=102</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] 계좌 파랗게 질려도 '월 500만원' 따박따박…폭락장 버틴 50대의 비결</t>
+          <t>[뉴스1] 수출 4강 '가시권'·소득 5만불 '환율 변수'…잠재성장 3%는 '험로'</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005386148?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009059814?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,11 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
     </font>
   </fonts>
   <fills count="2">
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -80,6 +85,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -476,72 +482,72 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] 윤석열 ‘유죄’ 나온 명태균 여론조사…김건희·오세훈에도 영향 미칠...</t>
+          <t>[서울신문] 민주 “즉각 재검표”… 국힘 “특검 먼저” “병행” 갈려</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458190?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003661217?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “집회 오라” 전화 거는 장동혁 측근들, 전화 피하는 의원들</t>
+          <t>[중앙일보] “盧 퇴임후 재수사 없게 해달라” 靑민정실 요구, 檢은 거부했다</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003537661?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003537658?sid=102</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 장동혁·정점식, 모처럼 '보완수사권' 한뜻… 한동훈까지 단일대오 움직...</t>
+          <t>[동아일보] 與 “투표지 247만장 즉각 재검표” 野 “특검 우선”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942308?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003734017?sid=102</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 오세훈 “서울 주택 행정은…” 李대통령 “그 얘기는 나중에 하시죠”</t>
+          <t>[조선일보] 국힘 소속 특위 위원장 “재검표를”… 국힘 특위 위원들은 “특검이 먼...</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987663?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/023/0003987666?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[조선일보] 버티던 정청래, 선호투표 수용… 친명 “동정표 노리고 선회”</t>
+          <t>[뉴스1] 與 "즉각 재검표"…野는 "특검과 병행"·"특검 먼저" 두 갈래(종합2보)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/023/0003987664?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009059721?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] 박범계 “정청래, 누구보다 사나워…스스로 약자 표현 적절치 않아”</t>
+          <t>[연합뉴스] 선관위 국조 '재검표' 합의 불발…與 "즉각"·국힘 "특검 우선"(종합)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002804698?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/001/0016194717?sid=100</t>
         </is>
       </c>
     </row>
@@ -553,124 +559,37 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] ‘조국당과 합당 무산’ 김민석에 화살 돌리는 정청래</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003733978?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>[이데일리] 정청래 “보완수사권 존치론 당황”…당 정체성·검찰개혁 강조</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006330307?sid=100</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>[뉴스1] 정청래, '보완수사권 일부 존치' 제기에 "정말 손 많이 가는 당"</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059665?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>[한국일보] [단독] 장동혁, 경기도당 위원장으로 '최측근' 조광한 띄우기, 당권파 세...</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000942299?sid=100</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] 장동혁, '재선거' 고리로 전국 돌며 지지층 확보 총력…오늘 광주행</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067055?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] 오세훈 “부동산 한말씀 드려도 되겠나” 한성숙 “서류로 받겠다”</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003733968?sid=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>4) 경제 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>[경향신문] [단독]4년 만에 도로 ‘컬러풀 대구’?···도시브랜드 교체에 또 수억...</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003458192?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] "교사·학생도 경제·금융 알아야"…서울교육청, 연수·수업 연계</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014067116?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>[뉴스1] 수출 4강 '가시권'·소득 5만불 '환율 변수'…잠재성장 3%는 '험로'</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009059814?sid=101</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>

--- a/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260715__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -551,43 +551,67 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>[연합뉴스] 與 "투표포기 인원도 파악못해"…국힘 "선피아 카르텔 드러나"(종합2보...</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/001/0016194712?sid=100</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[데일리안] 여야, 선관위 한목소리 질타…"투표 관리부터 전관 특혜까지 총체적 부...</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/119/0003111468?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2) 더불어민주당 동정</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
